--- a/Phytium_PPE_System_SourceCode/测试数据汇总-需求覆盖度.xlsx
+++ b/Phytium_PPE_System_SourceCode/测试数据汇总-需求覆盖度.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="10480"/>
+    <workbookView windowWidth="27950" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>测试数据汇总</t>
   </si>
@@ -123,6 +123,9 @@
   </si>
   <si>
     <t>主从核心跳通信</t>
+  </si>
+  <si>
+    <t>00</t>
   </si>
   <si>
     <t>REQ-13</t>
@@ -808,7 +811,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -821,9 +824,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -840,6 +840,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1386,8 +1389,8 @@
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
       <c r="F1" s="3" t="s">
         <v>2</v>
       </c>
@@ -1408,261 +1411,285 @@
       <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>50</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>50</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>0</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>50</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>47</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>3</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>0.94</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="8">
         <v>20</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>17</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>3</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <v>0.85</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>30</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>29</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="8">
         <v>1</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="9">
         <v>0.966</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="C7" s="8">
+        <v>30</v>
+      </c>
+      <c r="D7" s="8">
+        <v>24</v>
+      </c>
+      <c r="E7" s="8">
+        <v>6</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>30</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>30</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>0</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="8">
         <v>30</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="8">
         <v>30</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="8">
         <v>0</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>50</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>45</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="8">
         <v>5</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <v>0.9</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="8">
         <v>30</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="8">
         <v>30</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="8">
         <v>0</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>50</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>50</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="8">
         <v>0</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
+      <c r="C13" s="8">
+        <v>20</v>
+      </c>
+      <c r="D13" s="8">
+        <v>20</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0</v>
+      </c>
+      <c r="F13" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
+      <c r="C14" s="8">
+        <v>20</v>
+      </c>
+      <c r="D14" s="8">
+        <v>20</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="9">
+      <c r="B15" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="8">
         <v>30</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="8">
         <v>30</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="8">
         <v>0</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="9">
+      <c r="B16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="8">
         <v>30</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>30</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="8">
         <v>0</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <v>1</v>
       </c>
     </row>
